--- a/data/raw/NL_density.xlsx
+++ b/data/raw/NL_density.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evgenii\Documents\MATLAB\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Density parametrization\script\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39ED71B-946B-4391-88A6-9B0765A0808D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB97218-4895-4132-AAE6-27598BD93EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{BF203801-D0BC-4E4B-8A67-3933DCEF8B1B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BF203801-D0BC-4E4B-8A67-3933DCEF8B1B}"/>
   </bookViews>
   <sheets>
     <sheet name="density" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
